--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,7 +1681,7 @@
         <v>153409</v>
       </c>
       <c r="B10" t="n">
-        <v>89167</v>
+        <v>90332</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455241.8418914244</v>
+        <v>455242</v>
       </c>
       <c r="R10" t="n">
-        <v>6223030.068857063</v>
+        <v>6223030</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -1762,19 +1762,9 @@
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2011-09-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1807,37 +1797,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64964592</v>
+        <v>153419</v>
       </c>
       <c r="B11" t="n">
-        <v>90128</v>
+        <v>89167</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>477</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönticka</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Albatrellus cristatus</t>
+          <t>Craterellus cinereus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.:Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1888,7 +1878,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
+          <t>2011-09-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1898,17 +1888,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
+          <t>2011-09-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i bokbacken (äldre produktionsbokskog) ned mot Rännan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1934,10 +1919,144 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>Tony Svensson, Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>64964592</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90128</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Albatrellus cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.:Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>455241.8418914244</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6223030.068857063</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2016-10-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2016-10-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i bokbacken (äldre produktionsbokskog) ned mot Rännan.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>bokskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
           <t>Tony Svensson, Lennart Söderberg, Sofia Lund, Joachim Krumlinde</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Puggehatten inventeringshelg</t>
         </is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -1681,7 +1681,7 @@
         <v>153409</v>
       </c>
       <c r="B10" t="n">
-        <v>90332</v>
+        <v>90349</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,37 +1797,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>153419</v>
+        <v>64964592</v>
       </c>
       <c r="B11" t="n">
-        <v>89167</v>
+        <v>90128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>477</v>
+        <v>19</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Grönticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus cinereus</t>
+          <t>Albatrellus cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Donk</t>
+          <t>(Schaeff.:Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-09-26</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1888,12 +1888,17 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-09-26</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i bokbacken (äldre produktionsbokskog) ned mot Rännan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1919,144 +1924,10 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tony Svensson, Lennart Söderberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>64964592</v>
-      </c>
-      <c r="B12" t="n">
-        <v>90128</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>19</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grönticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Albatrellus cristatus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Schaeff.:Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>455241.8418914244</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6223030.068857063</v>
-      </c>
-      <c r="S12" t="n">
-        <v>100</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Kristianstad</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Oppmanna</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i bokbacken (äldre produktionsbokskog) ned mot Rännan.</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>bokskog</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
           <t>Tony Svensson, Lennart Söderberg, Sofia Lund, Joachim Krumlinde</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Puggehatten inventeringshelg</t>
         </is>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6902176</v>
+        <v>64964592</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>19</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Albatrellus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Schaeff.:Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvahallarna, bokskogssluttning, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455241.8418914244</v>
+        <v>455242</v>
       </c>
       <c r="R2" t="n">
-        <v>6223030.068857063</v>
+        <v>6223030</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i bokbacken (äldre produktionsbokskog) ned mot Rännan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,12 +770,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>produktionsbokskog</t>
+          <t>bokskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -788,63 +787,70 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tony Svensson, Lennart Söderberg, Sofia Lund, Joachim Krumlinde</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Puggehatten inventeringshelg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6902182</v>
+        <v>81249544</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>472</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Silkesspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius turgidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvahallarna, bokskogssluttning, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455241.8418914244</v>
+        <v>455164</v>
       </c>
       <c r="R3" t="n">
-        <v>6223030.068857063</v>
+        <v>6223049</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +874,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stort utspritt mycel eller flera små.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +893,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>produktionsbokskog</t>
+          <t>gallrad bokskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,55 +917,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7007091</v>
+        <v>120082407</v>
       </c>
       <c r="B4" t="n">
-        <v>87558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3483</v>
+        <v>472</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rutbläcksvamp</t>
+          <t>Silkesspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coprinopsis picacea</t>
+          <t>Cortinarius turgidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+          <t>Tjuvahallarna, Snärjet, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455241.8418914244</v>
+        <v>455145</v>
       </c>
       <c r="R4" t="n">
-        <v>6223030.068857063</v>
+        <v>6223035</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +993,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-10-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1013,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>bokskog</t>
+          <t>Bokskog med inslag av klibbal, ek, asp. Västsluttning mot sjökant.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1035,47 +1031,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81249544</v>
+        <v>153409</v>
       </c>
       <c r="B5" t="n">
-        <v>85532</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silkesspindling</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius turgidus</t>
+          <t>Craterellus cinereus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1086,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455163.9046233668</v>
+        <v>455242</v>
       </c>
       <c r="R5" t="n">
-        <v>6223049.263291189</v>
+        <v>6223030</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,27 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stort utspritt mycel eller flera små.</t>
+          <t>2011-09-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1127,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>gallrad bokskog</t>
+          <t>bokskog med enstaka andra trädslag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1169,15 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81249527</v>
+        <v>281466</v>
       </c>
       <c r="B6" t="n">
-        <v>86194</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455193.0628965225</v>
+        <v>455242</v>
       </c>
       <c r="R6" t="n">
-        <v>6223008.85688977</v>
+        <v>6223030</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,22 +1221,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1241,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>gallrad bokskog</t>
+          <t>bokskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1291,50 +1252,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Tony Svensson, Lennart Söderberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81249486</v>
+        <v>81249527</v>
       </c>
       <c r="B7" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221423</v>
+        <v>821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gulprickig vaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Hygrophorus chrysodon</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Batsch) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1342,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455241.8418914244</v>
+        <v>455193</v>
       </c>
       <c r="R7" t="n">
-        <v>6223030.068857063</v>
+        <v>6223009</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1375,19 +1338,9 @@
           <t>2019-09-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-09-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,64 +1373,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1764278</v>
+        <v>120081397</v>
       </c>
       <c r="B8" t="n">
-        <v>89172</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5678</v>
+        <v>821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kruskantarell</t>
+          <t>Gulprickig vaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus undulatus</t>
+          <t>Hygrophorus chrysodon</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Campo &amp; Papetti</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Batsch) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+          <t>Tjuvahallarna, Snärjet, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455241.8418914244</v>
+        <v>455136</v>
       </c>
       <c r="R8" t="n">
-        <v>6223030.068857063</v>
+        <v>6223044</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1501,22 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1461,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>bokskog med enstaka andra trädslag</t>
+          <t>Bokskog med inslag av klibbal, ek, asp. Västsluttning mot sjökant.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,64 +1479,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>281466</v>
+        <v>81249595</v>
       </c>
       <c r="B9" t="n">
-        <v>86194</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>821</v>
+        <v>1357</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulprickig vaxskivling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus chrysodon</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch) Fr.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+          <t>Tjuvahallarna, strandvallen, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455241.8418914244</v>
+        <v>455131</v>
       </c>
       <c r="R9" t="n">
-        <v>6223030.068857063</v>
+        <v>6223005</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1630,22 +1555,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-09-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-09-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,7 +1575,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>bokskog</t>
+          <t>sjövall med bok, klibbal</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,71 +1586,58 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tony Svensson, Lennart Söderberg</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>153409</v>
+        <v>81249803</v>
       </c>
       <c r="B10" t="n">
-        <v>90349</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>477</v>
+        <v>2979</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus cinereus</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+          <t>Tjuvahallarna, vägen, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455242</v>
+        <v>455511</v>
       </c>
       <c r="R10" t="n">
-        <v>6223030</v>
+        <v>6223040</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,12 +1661,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
+          <t>2019-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,7 +1681,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>bokskog med enstaka andra trädslag</t>
+          <t>ädellövskog med bok, ek</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1797,61 +1699,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64964592</v>
+        <v>7007091</v>
       </c>
       <c r="B11" t="n">
-        <v>90128</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>88540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>3483</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönticka</t>
+          <t>Rutbläcksvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Albatrellus cristatus</t>
+          <t>Coprinopsis picacea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.:Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvahallarna, bokskogssluttning, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455241.8418914244</v>
+        <v>455242</v>
       </c>
       <c r="R11" t="n">
-        <v>6223030.068857063</v>
+        <v>6223030</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1878,27 +1766,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i bokbacken (äldre produktionsbokskog) ned mot Rännan.</t>
+          <t>2013-10-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,14 +1797,671 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1764278</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91683</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5678</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kruskantarell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Craterellus undulatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Campo &amp; Papetti</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>455242</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6223030</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>bokskog med enstaka andra trädslag</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>55502542</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Snärjet. Oppmanna kyrka, 1,3 km väster, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>455158</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6223111</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2010-05-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2010-05-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>På hällmark mot sundet i Oppmannasjön</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson, Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6902176</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>455242</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6223030</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-08-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-08-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>produktionsbokskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>64964683</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>455242</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6223030</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2016-10-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2016-10-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>bokskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Tony Svensson, Lennart Söderberg, Sofia Lund, Joachim Krumlinde</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Puggehatten inventeringshelg</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6902182</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjuvahallarna, bokskogssluttning, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>455242</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6223030</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2013-08-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2013-08-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>produktionsbokskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>81249476</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91413</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>233194</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Laxfingersvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramaria flavosalmonicolor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schild, 1990</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Snärjet, bokblandskog, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>455283</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6223118</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-09-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sporer 7,5-8 x 3,5-4 um, cylindriska-ellipsoida, ibland konstrikta. Med söljor.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>bokblandskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53161-2023 artfynd.xlsx
+++ b/artfynd/A 53161-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
           <t>Puggehatten inventeringshelg</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64964592</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81249544</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120082407</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/153409</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/281466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81249527</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120081397</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81249595</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7007091</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1809,6 +1859,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1764278</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1914,6 +1969,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55502542</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2019,6 +2079,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6902176</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
           <t>Puggehatten inventeringshelg</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64964683</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2233,6 +2303,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6902182</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2356,6 +2431,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81249476</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2462,8 +2542,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81249803</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>